--- a/Heuristic/data/Starting_point.xlsx
+++ b/Heuristic/data/Starting_point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Heuristic/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98C0F0CD-4487-4EAF-8770-9D482198FB14}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C259262-6517-4957-BCCE-4EE5F2B0DB0F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -263,7 +263,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -289,6 +289,7 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -715,13 +716,13 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="14">
-        <v>1</v>
-      </c>
-      <c r="C13" s="14">
+      <c r="B13" s="15">
+        <v>1</v>
+      </c>
+      <c r="C13" s="15">
         <v>3</v>
       </c>
     </row>

--- a/Heuristic/data/Starting_point.xlsx
+++ b/Heuristic/data/Starting_point.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Heuristic/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C259262-6517-4957-BCCE-4EE5F2B0DB0F}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB28AB3E-8FB3-4370-B6E8-69B7D7BBDF15}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14180" yWindow="-6440" windowWidth="28800" windowHeight="15450" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -193,7 +193,7 @@
     <numFmt numFmtId="166" formatCode="0.000000"/>
     <numFmt numFmtId="167" formatCode="0.000000%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,12 +216,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFCE9178"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -263,7 +257,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -276,20 +270,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -628,101 +621,101 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14">
-        <v>1</v>
-      </c>
-      <c r="C5" s="14">
+      <c r="B5" s="11">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="14">
-        <v>1</v>
-      </c>
-      <c r="C6" s="14">
+      <c r="B6" s="11">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="14">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14">
+      <c r="B7" s="11">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="14">
-        <v>1</v>
-      </c>
-      <c r="C8" s="14">
+      <c r="B8" s="11">
+        <v>1</v>
+      </c>
+      <c r="C8" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="14">
-        <v>1</v>
-      </c>
-      <c r="C9" s="14">
+      <c r="B9" s="11">
+        <v>1</v>
+      </c>
+      <c r="C9" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="14">
-        <v>1</v>
-      </c>
-      <c r="C10" s="14">
+      <c r="B10" s="11">
+        <v>1</v>
+      </c>
+      <c r="C10" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="14">
-        <v>1</v>
-      </c>
-      <c r="C11" s="14">
+      <c r="B11" s="11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="14">
-        <v>1</v>
-      </c>
-      <c r="C12" s="14">
+      <c r="B12" s="11">
+        <v>1</v>
+      </c>
+      <c r="C12" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="15">
-        <v>1</v>
-      </c>
-      <c r="C13" s="15">
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
         <v>3</v>
       </c>
     </row>
@@ -1220,151 +1213,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="8">
-        <v>137010500</v>
+      <c r="B2" s="12">
+        <v>398056107.80000001</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="8">
-        <v>283717500</v>
+      <c r="B3" s="12">
+        <v>27968660.210000001</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B4" s="12">
-        <v>9879500</v>
+        <v>410128001.42000002</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="12">
-        <v>108804000</v>
+        <v>590379508</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="11">
-        <v>500</v>
-      </c>
-      <c r="D6" s="8"/>
+      <c r="B6" s="13">
+        <v>280763726</v>
+      </c>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="11">
-        <v>1000</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="9"/>
+      <c r="B7" s="13">
+        <v>879375105</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="11">
-        <v>350</v>
-      </c>
-      <c r="E8" s="9"/>
+      <c r="B8" s="13">
+        <v>83171840</v>
+      </c>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B9" s="12">
-        <v>10000000</v>
+        <v>7682600</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="14" t="s">
         <v>40</v>
       </c>
       <c r="B10" s="12">
-        <v>10000000</v>
+        <v>3278988.3</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="12">
-        <v>10000000</v>
+        <v>2828944.58</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="14" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="12">
-        <v>10000000</v>
+        <v>116834378.34999999</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="14" t="s">
         <v>27</v>
       </c>
       <c r="B13" s="12">
-        <v>143856000</v>
+        <v>5298997.59</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="14" t="s">
         <v>42</v>
       </c>
       <c r="B14" s="12">
-        <v>10000000</v>
+        <v>30290394.390000001</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="14" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="12">
-        <v>10000000</v>
+        <v>43271991.979999997</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B16" s="12">
-        <v>43714500</v>
+        <v>86543983.959999993</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="14" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="12">
-        <v>9216211.8592507206</v>
+        <v>242285505</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B18" s="12">
-        <v>67456638.140749902</v>
+        <v>156726900</v>
       </c>
     </row>
   </sheetData>
@@ -1394,7 +1387,7 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>109769715.256769</v>
       </c>
     </row>
@@ -1402,7 +1395,7 @@
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>76483381.4640522</v>
       </c>
     </row>
@@ -1410,7 +1403,7 @@
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>111936141.058823</v>
       </c>
     </row>
@@ -1418,7 +1411,7 @@
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>6763202.4705882296</v>
       </c>
     </row>
@@ -1426,7 +1419,7 @@
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>50081880.540420704</v>
       </c>
     </row>
@@ -1434,7 +1427,7 @@
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>59034355.4808589</v>
       </c>
     </row>
@@ -1442,7 +1435,7 @@
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>171888397.557423</v>
       </c>
     </row>
@@ -1450,7 +1443,7 @@
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>52857961.247619003</v>
       </c>
     </row>
@@ -1458,7 +1451,7 @@
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>63880730.2712842</v>
       </c>
     </row>
@@ -1466,7 +1459,7 @@
       <c r="A11" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>106632842.278244</v>
       </c>
     </row>
@@ -1474,7 +1467,7 @@
       <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>148000000</v>
       </c>
     </row>
@@ -1482,7 +1475,7 @@
       <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>21600000</v>
       </c>
     </row>
